--- a/config/explorer/explorer.xlsx
+++ b/config/explorer/explorer.xlsx
@@ -1146,10 +1146,6 @@
         </is>
       </c>
       <c r="B2" s="1" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
           <t>config/explorer/test_qpp.png</t>
@@ -1294,23 +1290,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr"/>
       <c r="B4" s="1" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1320,7 +1300,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>初号機-α</t>
+          <t>初号机-α</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1581,7 +1561,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>砲撃型-β</t>
+          <t>炮击型-β</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1755,7 +1735,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>機動型-γ</t>
+          <t>机动型-γ</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1842,7 +1822,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>飛行型-γ</t>
+          <t>飞行型-γ</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -2016,7 +1996,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>究極型-δ</t>
+          <t>终极型-δ</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
